--- a/data/categories.xlsx
+++ b/data/categories.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,13 +415,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2" t="str">
-        <v>默认类别</v>
+        <v>多媒体互动</v>
       </c>
       <c r="C2" t="str">
-        <v>默认类别</v>
+        <v>多媒体互动</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -429,21 +429,63 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B3" t="str">
-        <v>你好</v>
+        <v>数字人</v>
       </c>
       <c r="C3" t="str">
-        <v>你好</v>
+        <v>数字人</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>6</v>
+      </c>
+      <c r="B4" t="str">
+        <v>大熊猫星团数字艺术展</v>
+      </c>
+      <c r="C4" t="str">
+        <v>大熊猫星团数字艺术展</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>7</v>
+      </c>
+      <c r="B5" t="str">
+        <v>大空间VR</v>
+      </c>
+      <c r="C5" t="str">
+        <v>大空间VR</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>8</v>
+      </c>
+      <c r="B6" t="str">
+        <v>AR</v>
+      </c>
+      <c r="C6" t="str">
+        <v>AR</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>